--- a/cơ sinh/whack-a-mole-hand-control/src/game_history.xlsx
+++ b/cơ sinh/whack-a-mole-hand-control/src/game_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -506,6 +506,195 @@
         <v>80</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2025-10-24 21:03:01</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>we</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2025-10-24 21:03:48</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>we 1</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2025-10-24 21:14:22</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2025-10-24 21:17:34</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>nd</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2025-10-24 21:31:00</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>dc</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2025-10-24 21:31:38</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>fv</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2025-10-24 21:32:29</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2025-10-25 09:22:03</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>aa</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2025-10-27 09:47:05</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>nn</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
